--- a/templates/forms/medical_care_coordination_sheet.xlsx
+++ b/templates/forms/medical_care_coordination_sheet.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CareManagementTool\templates\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB548BEE-9823-4D69-A79A-514BBE00108D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C96EA4-48E2-40A8-8594-C2DA9C007EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15750" xr2:uid="{DBAD6EAE-E3D3-4817-A49D-7493304547F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DBAD6EAE-E3D3-4817-A49D-7493304547F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1511,17 +1508,236 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -1530,9 +1746,6 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1542,227 +1755,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2123,65 +2117,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="救急医療情報"/>
-      <sheetName val="チェックシート"/>
-      <sheetName val="HOME"/>
-      <sheetName val="（最新）アセスメントシート"/>
-      <sheetName val="居宅届"/>
-      <sheetName val="居宅届 (予防)"/>
-      <sheetName val="フェースシート"/>
-      <sheetName val="医療・介護連携シート"/>
-      <sheetName val="(貼付作成)入院時情報提供"/>
-      <sheetName val="(手入力)入院時情報提供"/>
-      <sheetName val="モニタリングシート"/>
-      <sheetName val="担会案内"/>
-      <sheetName val="更新・新規申請書"/>
-      <sheetName val="区分変更申請書 "/>
-      <sheetName val="資料提供申請書"/>
-      <sheetName val="確認書（原本）"/>
-      <sheetName val="入退去連絡"/>
-      <sheetName val="リスト"/>
-      <sheetName val="確認書（ヘルパー）"/>
-      <sheetName val="確認書（デイ）"/>
-      <sheetName val="確認書（福祉用具）"/>
-    </sheetNames>
-    <definedNames>
-      <definedName name="A4両面印刷"/>
-    </definedNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -2485,1005 +2420,1021 @@
   <dimension ref="A1:T52"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="20" width="4.625" style="6" customWidth="1"/>
+    <col min="1" max="20" width="4.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="3" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-    </row>
-    <row r="2" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-    </row>
-    <row r="3" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="4" t="s">
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+    </row>
+    <row r="2" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+    </row>
+    <row r="3" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="5">
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="78">
         <f ca="1">TODAY()</f>
-        <v>45979</v>
-      </c>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-    </row>
-    <row r="4" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="7" t="s">
+        <v>46152</v>
+      </c>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+    </row>
+    <row r="4" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10"/>
-      <c r="J4" s="11" t="s">
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="4"/>
+      <c r="J4" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="13" t="s">
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="14"/>
-    </row>
-    <row r="5" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="15"/>
-      <c r="C5" s="16" t="s">
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="82"/>
+    </row>
+    <row r="5" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5"/>
+      <c r="C5" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="18"/>
-      <c r="J5" s="19" t="s">
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="2"/>
+      <c r="J5" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="20">
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="73">
         <v>2472400072</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="21"/>
-    </row>
-    <row r="6" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="19" t="s">
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="74"/>
+    </row>
+    <row r="6" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="67"/>
+      <c r="C6" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="J6" s="22" t="s">
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="2"/>
+      <c r="J6" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="23"/>
-      <c r="L6" s="16" t="s">
+      <c r="K6" s="70"/>
+      <c r="L6" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="17"/>
-    </row>
-    <row r="7" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="19" t="s">
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="72"/>
+    </row>
+    <row r="7" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="20" t="s">
+      <c r="B7" s="67"/>
+      <c r="C7" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="18"/>
-      <c r="J7" s="22" t="s">
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="2"/>
+      <c r="J7" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="20" t="s">
+      <c r="K7" s="70"/>
+      <c r="L7" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="24" t="s">
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="20" t="s">
+      <c r="P7" s="75"/>
+      <c r="Q7" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="21"/>
-    </row>
-    <row r="8" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="19" t="s">
+      <c r="R7" s="73"/>
+      <c r="S7" s="73"/>
+      <c r="T7" s="74"/>
+    </row>
+    <row r="8" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="67"/>
+      <c r="C8" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="18"/>
-      <c r="J8" s="22" t="s">
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="2"/>
+      <c r="J8" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="17"/>
-    </row>
-    <row r="9" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="15"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="18"/>
-      <c r="J9" s="22" t="s">
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="72"/>
+    </row>
+    <row r="9" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="5"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="2"/>
+      <c r="J9" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="27" t="s">
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="T9" s="28"/>
-    </row>
-    <row r="10" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="29"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="31" t="s">
+      <c r="T9" s="8"/>
+    </row>
+    <row r="10" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="18"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="33"/>
-    </row>
-    <row r="11" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
+      <c r="G10" s="36"/>
+      <c r="H10" s="2"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="11"/>
+    </row>
+    <row r="11" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="76" t="s">
+    <row r="14" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="76"/>
-      <c r="C15" s="6" t="s">
+    <row r="15" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="23"/>
+      <c r="C15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="76" t="s">
+    <row r="16" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="34" t="s">
+    <row r="18" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37" t="s">
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="38"/>
-      <c r="S18" s="38"/>
-      <c r="T18" s="39"/>
-    </row>
-    <row r="19" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="40" t="s">
+      <c r="I18" s="55"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="13"/>
+    </row>
+    <row r="19" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="45"/>
-      <c r="P19" s="46" t="s">
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="6" t="s">
+      <c r="Q19" s="2"/>
+      <c r="R19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="T19" s="28"/>
-    </row>
-    <row r="20" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="47"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="33"/>
-    </row>
-    <row r="21" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="52" t="s">
+      <c r="T19" s="8"/>
+    </row>
+    <row r="20" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="59"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="11"/>
+    </row>
+    <row r="21" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53" t="s">
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="55" t="s">
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="56"/>
-    </row>
-    <row r="22" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="57" t="s">
+      <c r="P21" s="39"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="40"/>
+    </row>
+    <row r="22" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="59" t="s">
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="58"/>
-      <c r="S22" s="58"/>
-      <c r="T22" s="60"/>
-    </row>
-    <row r="23" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="61"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="62"/>
-      <c r="T23" s="64"/>
-    </row>
-    <row r="24" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="6" t="s">
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="47"/>
+    </row>
+    <row r="23" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="42"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="44"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="48"/>
+    </row>
+    <row r="24" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="65" t="s">
+    <row r="25" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="66" t="s">
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="67"/>
-      <c r="L25" s="77" t="s">
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="M25" s="67" t="s">
+      <c r="M25" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="N25" s="67"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="77" t="s">
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="Q25" s="67" t="s">
+      <c r="Q25" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="R25" s="67"/>
-      <c r="S25" s="67"/>
-      <c r="T25" s="68"/>
-    </row>
-    <row r="26" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="75" t="s">
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="18"/>
+    </row>
+    <row r="26" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J26" s="75" t="s">
+      <c r="J26" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="T26" s="28"/>
-    </row>
-    <row r="27" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="75" t="s">
+      <c r="T26" s="8"/>
+    </row>
+    <row r="27" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J27" s="75" t="s">
+      <c r="J27" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="T27" s="28"/>
-    </row>
-    <row r="28" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="75" t="s">
+      <c r="T27" s="8"/>
+    </row>
+    <row r="28" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J28" s="75" t="s">
+      <c r="J28" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="T28" s="28"/>
-    </row>
-    <row r="29" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="75" t="s">
+      <c r="T28" s="8"/>
+    </row>
+    <row r="29" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="75" t="s">
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="K29" s="30" t="s">
+      <c r="K29" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="33"/>
-    </row>
-    <row r="30" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="69" t="s">
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="11"/>
+    </row>
+    <row r="30" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="70"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="38"/>
-      <c r="L30" s="38"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="38"/>
-      <c r="P30" s="38"/>
-      <c r="Q30" s="38"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="38"/>
-      <c r="T30" s="39"/>
-    </row>
-    <row r="31" spans="1:20" s="6" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="78"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="79"/>
-      <c r="K31" s="79"/>
-      <c r="L31" s="79"/>
-      <c r="M31" s="79"/>
-      <c r="N31" s="79"/>
-      <c r="O31" s="79"/>
-      <c r="P31" s="79"/>
-      <c r="Q31" s="79"/>
-      <c r="R31" s="79"/>
-      <c r="S31" s="79"/>
-      <c r="T31" s="80"/>
-    </row>
-    <row r="32" spans="1:20" s="6" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="81"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="79"/>
-      <c r="K32" s="79"/>
-      <c r="L32" s="79"/>
-      <c r="M32" s="79"/>
-      <c r="N32" s="79"/>
-      <c r="O32" s="79"/>
-      <c r="P32" s="79"/>
-      <c r="Q32" s="79"/>
-      <c r="R32" s="79"/>
-      <c r="S32" s="79"/>
-      <c r="T32" s="80"/>
-    </row>
-    <row r="33" spans="1:20" s="6" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="81"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="79"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="79"/>
-      <c r="N33" s="79"/>
-      <c r="O33" s="79"/>
-      <c r="P33" s="79"/>
-      <c r="Q33" s="79"/>
-      <c r="R33" s="79"/>
-      <c r="S33" s="79"/>
-      <c r="T33" s="80"/>
-    </row>
-    <row r="34" spans="1:20" s="6" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="81"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="79"/>
-      <c r="M34" s="79"/>
-      <c r="N34" s="79"/>
-      <c r="O34" s="79"/>
-      <c r="P34" s="79"/>
-      <c r="Q34" s="79"/>
-      <c r="R34" s="79"/>
-      <c r="S34" s="79"/>
-      <c r="T34" s="80"/>
-    </row>
-    <row r="35" spans="1:20" s="6" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="81"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
-      <c r="I35" s="79"/>
-      <c r="J35" s="79"/>
-      <c r="K35" s="79"/>
-      <c r="L35" s="79"/>
-      <c r="M35" s="79"/>
-      <c r="N35" s="79"/>
-      <c r="O35" s="79"/>
-      <c r="P35" s="79"/>
-      <c r="Q35" s="79"/>
-      <c r="R35" s="79"/>
-      <c r="S35" s="79"/>
-      <c r="T35" s="80"/>
-    </row>
-    <row r="36" spans="1:20" s="6" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="81"/>
-      <c r="B36" s="79"/>
-      <c r="C36" s="79"/>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
-      <c r="I36" s="79"/>
-      <c r="J36" s="79"/>
-      <c r="K36" s="79"/>
-      <c r="L36" s="79"/>
-      <c r="M36" s="79"/>
-      <c r="N36" s="79"/>
-      <c r="O36" s="79"/>
-      <c r="P36" s="79"/>
-      <c r="Q36" s="79"/>
-      <c r="R36" s="79"/>
-      <c r="S36" s="79"/>
-      <c r="T36" s="80"/>
-    </row>
-    <row r="37" spans="1:20" s="6" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="81"/>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="79"/>
-      <c r="I37" s="79"/>
-      <c r="J37" s="79"/>
-      <c r="K37" s="79"/>
-      <c r="L37" s="79"/>
-      <c r="M37" s="79"/>
-      <c r="N37" s="79"/>
-      <c r="O37" s="79"/>
-      <c r="P37" s="79"/>
-      <c r="Q37" s="79"/>
-      <c r="R37" s="79"/>
-      <c r="S37" s="79"/>
-      <c r="T37" s="80"/>
-    </row>
-    <row r="38" spans="1:20" s="6" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="81"/>
-      <c r="B38" s="79"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="79"/>
-      <c r="J38" s="79"/>
-      <c r="K38" s="79"/>
-      <c r="L38" s="79"/>
-      <c r="M38" s="79"/>
-      <c r="N38" s="79"/>
-      <c r="O38" s="79"/>
-      <c r="P38" s="79"/>
-      <c r="Q38" s="79"/>
-      <c r="R38" s="79"/>
-      <c r="S38" s="79"/>
-      <c r="T38" s="80"/>
-    </row>
-    <row r="39" spans="1:20" s="6" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="29"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30" t="s">
+      <c r="B30" s="29"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="13"/>
+    </row>
+    <row r="31" spans="1:20" s="3" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="31"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
+      <c r="O31" s="32"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="33"/>
+    </row>
+    <row r="32" spans="1:20" s="3" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="34"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="33"/>
+    </row>
+    <row r="33" spans="1:20" s="3" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="34"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="33"/>
+    </row>
+    <row r="34" spans="1:20" s="3" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="34"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="32"/>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="33"/>
+    </row>
+    <row r="35" spans="1:20" s="3" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="34"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="33"/>
+    </row>
+    <row r="36" spans="1:20" s="3" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="34"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="33"/>
+    </row>
+    <row r="37" spans="1:20" s="3" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="34"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="33"/>
+    </row>
+    <row r="38" spans="1:20" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="34"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="32"/>
+      <c r="T38" s="33"/>
+    </row>
+    <row r="39" spans="1:20" s="3" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="9"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="32"/>
-    </row>
-    <row r="40" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="6" t="s">
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="35"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="35"/>
+      <c r="Q39" s="35"/>
+      <c r="R39" s="35"/>
+      <c r="S39" s="35"/>
+      <c r="T39" s="36"/>
+    </row>
+    <row r="40" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="65" t="s">
+    <row r="41" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="38"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="38"/>
-      <c r="K41" s="38"/>
-      <c r="L41" s="38"/>
-      <c r="M41" s="38"/>
-      <c r="N41" s="38"/>
-      <c r="O41" s="38"/>
-      <c r="P41" s="38"/>
-      <c r="Q41" s="38"/>
-      <c r="R41" s="38"/>
-      <c r="S41" s="38"/>
-      <c r="T41" s="39"/>
-    </row>
-    <row r="42" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="75" t="s">
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="12"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="12"/>
+      <c r="P41" s="12"/>
+      <c r="Q41" s="12"/>
+      <c r="R41" s="12"/>
+      <c r="S41" s="12"/>
+      <c r="T41" s="13"/>
+    </row>
+    <row r="42" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="T42" s="28"/>
-    </row>
-    <row r="43" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="75" t="s">
+      <c r="T42" s="8"/>
+    </row>
+    <row r="43" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="T43" s="28"/>
-    </row>
-    <row r="44" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="75" t="s">
+      <c r="T43" s="8"/>
+    </row>
+    <row r="44" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="T44" s="28"/>
-    </row>
-    <row r="45" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="75" t="s">
+      <c r="T44" s="8"/>
+    </row>
+    <row r="45" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B45" s="83" t="s">
+      <c r="B45" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="82" t="s">
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="I45" s="30" t="s">
+      <c r="I45" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="J45" s="30"/>
-      <c r="K45" s="30"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="30"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="30"/>
-      <c r="Q45" s="30"/>
-      <c r="R45" s="30"/>
-      <c r="S45" s="30"/>
-      <c r="T45" s="33"/>
-    </row>
-    <row r="46" spans="1:20" s="6" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="69" t="s">
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="11"/>
+    </row>
+    <row r="46" spans="1:20" s="3" customFormat="1" ht="15.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B46" s="70"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
-      <c r="J46" s="38"/>
-      <c r="K46" s="38"/>
-      <c r="L46" s="38"/>
-      <c r="M46" s="38"/>
-      <c r="N46" s="38"/>
-      <c r="O46" s="38"/>
-      <c r="P46" s="38"/>
-      <c r="Q46" s="38"/>
-      <c r="R46" s="38"/>
-      <c r="S46" s="38"/>
-      <c r="T46" s="39"/>
-    </row>
-    <row r="47" spans="1:20" s="6" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="15"/>
-      <c r="T47" s="28"/>
-    </row>
-    <row r="48" spans="1:20" s="6" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="72"/>
-      <c r="B48" s="73"/>
-      <c r="C48" s="73"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="73"/>
-      <c r="K48" s="73"/>
-      <c r="L48" s="73"/>
-      <c r="M48" s="73"/>
-      <c r="N48" s="73"/>
-      <c r="O48" s="73"/>
-      <c r="P48" s="73"/>
-      <c r="Q48" s="73"/>
-      <c r="R48" s="73"/>
-      <c r="S48" s="73"/>
-      <c r="T48" s="74"/>
-    </row>
-    <row r="49" spans="1:20" s="6" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="15"/>
-      <c r="T49" s="28"/>
-    </row>
-    <row r="50" spans="1:20" s="6" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="72"/>
-      <c r="B50" s="73"/>
-      <c r="C50" s="73"/>
-      <c r="D50" s="73"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="73"/>
-      <c r="G50" s="73"/>
-      <c r="H50" s="73"/>
-      <c r="I50" s="73"/>
-      <c r="J50" s="73"/>
-      <c r="K50" s="73"/>
-      <c r="L50" s="73"/>
-      <c r="M50" s="73"/>
-      <c r="N50" s="73"/>
-      <c r="O50" s="73"/>
-      <c r="P50" s="73"/>
-      <c r="Q50" s="73"/>
-      <c r="R50" s="73"/>
-      <c r="S50" s="73"/>
-      <c r="T50" s="74"/>
-    </row>
-    <row r="51" spans="1:20" s="6" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="29"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30" t="s">
+      <c r="B46" s="29"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="12"/>
+      <c r="R46" s="12"/>
+      <c r="S46" s="12"/>
+      <c r="T46" s="13"/>
+    </row>
+    <row r="47" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="5"/>
+      <c r="T47" s="8"/>
+    </row>
+    <row r="48" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="19"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="20"/>
+      <c r="S48" s="20"/>
+      <c r="T48" s="21"/>
+    </row>
+    <row r="49" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="5"/>
+      <c r="T49" s="8"/>
+    </row>
+    <row r="50" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="19"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
+      <c r="S50" s="20"/>
+      <c r="T50" s="21"/>
+    </row>
+    <row r="51" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="30"/>
-      <c r="K51" s="30"/>
-      <c r="L51" s="30"/>
-      <c r="M51" s="30"/>
-      <c r="N51" s="30"/>
-      <c r="O51" s="30"/>
-      <c r="P51" s="30"/>
-      <c r="Q51" s="30"/>
-      <c r="R51" s="30"/>
-      <c r="S51" s="30"/>
-      <c r="T51" s="33"/>
-    </row>
-    <row r="52" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="E52" s="6" t="s">
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="11"/>
+    </row>
+    <row r="52" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="E52" s="3" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:T38"/>
-    <mergeCell ref="N39:T39"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:N21"/>
-    <mergeCell ref="P21:T21"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:T6"/>
+    <mergeCell ref="A1:G3"/>
+    <mergeCell ref="J1:T2"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:S3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="N4:T4"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="N5:T5"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G9"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="M8:T8"/>
+    <mergeCell ref="J9:P9"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B22:J23"/>
     <mergeCell ref="K22:K23"/>
@@ -3496,32 +3447,16 @@
     <mergeCell ref="C19:G20"/>
     <mergeCell ref="J19:O19"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G9"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="M8:T8"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="N5:T5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:T6"/>
-    <mergeCell ref="A1:G3"/>
-    <mergeCell ref="J1:T2"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N3:S3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="N4:T4"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:N21"/>
+    <mergeCell ref="P21:T21"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:T38"/>
+    <mergeCell ref="N39:T39"/>
+    <mergeCell ref="A46:C46"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
